--- a/excel-files/CALOOCAN/ANDRES BONIFACIO ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/ANDRES BONIFACIO ELEMENTARY SCHOOL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="360" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E3791A65-052C-4DDE-A0F8-CA6282C9405E}"/>
+  <xr:revisionPtr revIDLastSave="431" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CD7BA478-5C41-4A47-8BF5-90330763E51E}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LAS" sheetId="4" r:id="rId1"/>
@@ -11628,18 +11628,21 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 R103:R110 R83:R91 R93:R101 R14:R21 R5:R12 X103:X110 L103:L110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 F93:F101 F83:F91 F63:F71 F73:F81 F103:F110 F112:F127" xr:uid="{087FAB5B-5EA5-41CA-A1C7-AB77BBE643AE}">
       <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61 L63:L71 L73:L81 L83:L91 L93:L101 L103:L110 L112:L127 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 R63:R71 R73:R81 R83:R91 R93:R101 R103:R110 R112:R127 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 X63:X71 X73:X81 X83:X91 X93:X101 X103:X110" xr:uid="{E42A3E12-BE87-429C-89EE-035FB6A40747}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20250,15 +20253,21 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 X115:X122 R115:R122 L115:L122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F43:F53 F31:F41 F21:F29 F3:F10 F12:F19 F55:F65 F103:F113 F91:F101 F67:F77 F79:F89 F115:F122" xr:uid="{50361E96-8DC4-485A-8166-4BA4DEDDACC5}">
       <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19" xr:uid="{A41997CB-33EC-4C84-B095-D59B5EAA223F}">
+      <formula1>"2024,2025 ,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{7DDECA79-2D27-437C-926A-25C8F19BF9FF}">
+      <formula1>"2024,2025 ,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
